--- a/data/trending_integrated_20261013_09.xlsx
+++ b/data/trending_integrated_20261013_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42650</v>
+        <v>43450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'-3.94%</t>
+          <t>'-2.14%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.23</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G2" t="n">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="H2" t="n">
         <v>13.1</v>
@@ -601,7 +601,7 @@
         <v>43300</v>
       </c>
       <c r="L2" t="n">
-        <v>43300</v>
+        <v>43500</v>
       </c>
       <c r="M2" t="n">
         <v>42500</v>
@@ -610,7 +610,7 @@
         <v>13.33</v>
       </c>
       <c r="O2" t="n">
-        <v>1396273075</v>
+        <v>3649690075</v>
       </c>
       <c r="P2" t="n">
         <v>69200</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>간암 1차 승인 기대감 및 공매도 세력에 대한 경계감 혼재. 한국 증시 전반의 약세 속 주가 변동성 예상.</t>
+          <t>신약 승인 가능성에 대한 기대감이 존재하나, 악성 매물대 소화 및 주가 하락에 대한 우려도 함께 제기되었습니다. 공매도 관련 언급도 확인되었습니다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', '공매도']</t>
+          <t>['신약 승인', '악성 매물대', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,60 +655,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14650</v>
+        <v>15500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-3.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="H3" t="n">
-        <v>3.43</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>15720</v>
+        <v>16090</v>
       </c>
       <c r="K3" t="n">
-        <v>14770</v>
+        <v>15190</v>
       </c>
       <c r="L3" t="n">
-        <v>14970</v>
+        <v>15830</v>
       </c>
       <c r="M3" t="n">
-        <v>14420</v>
+        <v>15100</v>
       </c>
       <c r="N3" t="n">
-        <v>3.37</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>5877078760</v>
+        <v>8360011845</v>
       </c>
       <c r="P3" t="n">
-        <v>31500</v>
+        <v>40350</v>
       </c>
       <c r="Q3" t="n">
-        <v>1272</v>
+        <v>3320</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 및 국내 증시 전반의 불안감 속 대한광통신 주가 하락 우려. 3분기 매출액 및 영업이익 증가 확인.</t>
+          <t>주가 하락에 대한 우려와 함께 스팸성 게시글에 대한 불만이 제기되었고, 일부 공매도 관련 언급이 있었습니다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['광케이블', '어닝 서프라이즈', '추세 하락']</t>
+          <t>['주가 하락', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -739,6 +739,466 @@
         </is>
       </c>
       <c r="Z3" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>68800</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'-3.78%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E4" t="n">
+        <v>117</v>
+      </c>
+      <c r="F4" t="n">
+        <v>93</v>
+      </c>
+      <c r="G4" t="n">
+        <v>408</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>71500</v>
+      </c>
+      <c r="K4" t="n">
+        <v>68400</v>
+      </c>
+      <c r="L4" t="n">
+        <v>69900</v>
+      </c>
+      <c r="M4" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="O4" t="n">
+        <v>23524261150</v>
+      </c>
+      <c r="P4" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 주가 하락에 대한 부정적인 게시글이 주를 이루었으며, 일부 신용 관련 언급과 함께 주가 전망이 제시되었습니다.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['주가 하락', '신용']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>239000</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'-4.59%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>800</v>
+      </c>
+      <c r="F5" t="n">
+        <v>539</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1736</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>250500</v>
+      </c>
+      <c r="K5" t="n">
+        <v>241500</v>
+      </c>
+      <c r="L5" t="n">
+        <v>244000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>238000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="O5" t="n">
+        <v>510705259000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 관련된 부정적인 게시글이 다수 확인되었으며, 거시 경제 전반에 대한 비관적인 전망이 제시되었습니다.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1523000</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'-5.11%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E6" t="n">
+        <v>800</v>
+      </c>
+      <c r="F6" t="n">
+        <v>532</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1990</v>
+      </c>
+      <c r="H6" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1519000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>665814277000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>정치적 요인과 관련된 부정적인 언급이 지배적이며, 증시 붕괴 및 주가 폭락에 대한 비관적인 전망이 다수 확인되었습니다.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['증시 붕괴', '주가 폭락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>금호타이어</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6460</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'-5.14%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45</v>
+      </c>
+      <c r="G7" t="n">
+        <v>193</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6810</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7150</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7160</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6450</v>
+      </c>
+      <c r="N7" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8267694020</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8850</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4220</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>공매도 관련 언급과 함께 주가 상승에 대한 기대감이 나타났으며, 일부 뉴스를 근거로 제시했습니다.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['공매도', '주가 상승']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>073240</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14840</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'-5.60%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>44</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>154</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>15720</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14770</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15060</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14420</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O8" t="n">
+        <v>18880768220</v>
+      </c>
+      <c r="P8" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>미국 업체 기술력 및 AI 거품론 언급과 함께 주가 하락에 대한 우려가 제기되었으며, 일부 실적 관련 긍정적 언급도 있었습니다.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['기술력', 'AI 거품론', '실적']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>010170</t>
         </is>

--- a/data/trending_integrated_20261013_09.xlsx
+++ b/data/trending_integrated_20261013_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43450</v>
+        <v>8780</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'-2.14%</t>
+          <t>'+29.88%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.23</v>
+        <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>371</v>
+        <v>117</v>
       </c>
       <c r="H2" t="n">
-        <v>13.1</v>
+        <v>1.84</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>44400</v>
+        <v>6760</v>
       </c>
       <c r="K2" t="n">
-        <v>43300</v>
+        <v>7530</v>
       </c>
       <c r="L2" t="n">
-        <v>43500</v>
+        <v>8780</v>
       </c>
       <c r="M2" t="n">
-        <v>42500</v>
+        <v>7250</v>
       </c>
       <c r="N2" t="n">
-        <v>13.33</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>3649690075</v>
+        <v>78898036450</v>
       </c>
       <c r="P2" t="n">
-        <v>69200</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>24150</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>신약 승인 가능성에 대한 기대감이 존재하나, 악성 매물대 소화 및 주가 하락에 대한 우려도 함께 제기되었습니다. 공매도 관련 언급도 확인되었습니다.</t>
+          <t>호남 반도체 투자 관련 수혜주로 서산의 주가 상승 기대감 및 긍정적 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['신약 승인', '악성 매물대', '공매도']</t>
+          <t>['호남 반도체', '수혜주', '주가 상승']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,67 +648,67 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15500</v>
+        <v>43550</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-3.67%</t>
+          <t>'-1.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>115</v>
+        <v>395</v>
       </c>
       <c r="H3" t="n">
-        <v>9.630000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>16090</v>
+        <v>44400</v>
       </c>
       <c r="K3" t="n">
-        <v>15190</v>
+        <v>43300</v>
       </c>
       <c r="L3" t="n">
-        <v>15830</v>
+        <v>44100</v>
       </c>
       <c r="M3" t="n">
-        <v>15100</v>
+        <v>42500</v>
       </c>
       <c r="N3" t="n">
-        <v>9.470000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="O3" t="n">
-        <v>8360011845</v>
+        <v>5559327675</v>
       </c>
       <c r="P3" t="n">
-        <v>40350</v>
+        <v>69200</v>
       </c>
       <c r="Q3" t="n">
-        <v>3320</v>
+        <v>24150</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -718,20 +718,20 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 우려와 함께 스팸성 게시글에 대한 불만이 제기되었고, 일부 공매도 관련 언급이 있었습니다.</t>
+          <t>HLB의 간암 1차 승인 기대감과 공매도 세력에 대한 언급, 긍정적 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도']</t>
+          <t>['간암 1차 승인', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68800</v>
+        <v>6630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-3.78%</t>
+          <t>'-2.64%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>-0.3</v>
       </c>
       <c r="E4" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>408</v>
+        <v>235</v>
       </c>
       <c r="H4" t="n">
-        <v>22.1</v>
+        <v>12.27</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,28 +779,28 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>71500</v>
+        <v>6810</v>
       </c>
       <c r="K4" t="n">
-        <v>68400</v>
+        <v>7150</v>
       </c>
       <c r="L4" t="n">
-        <v>69900</v>
+        <v>7160</v>
       </c>
       <c r="M4" t="n">
-        <v>68000</v>
+        <v>6440</v>
       </c>
       <c r="N4" t="n">
-        <v>22.21</v>
+        <v>12.57</v>
       </c>
       <c r="O4" t="n">
-        <v>23524261150</v>
+        <v>9887777415</v>
       </c>
       <c r="P4" t="n">
-        <v>139200</v>
+        <v>8850</v>
       </c>
       <c r="Q4" t="n">
-        <v>57000</v>
+        <v>4220</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치적 이슈와 주가 하락에 대한 부정적인 게시글이 주를 이루었으며, 일부 신용 관련 언급과 함께 주가 전망이 제시되었습니다.</t>
+          <t>금호타이어 주가 부양에 대한 기대감과 공매도 세력에 대한 비판.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주가 하락', '신용']</t>
+          <t>['공매도', '부양']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>239000</v>
+        <v>17530</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-4.59%</t>
+          <t>'-2.67%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.05</v>
+        <v>0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>539</v>
+        <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>1736</v>
+        <v>154</v>
       </c>
       <c r="H5" t="n">
-        <v>46.3</v>
+        <v>27.69</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>250500</v>
+        <v>18010</v>
       </c>
       <c r="K5" t="n">
-        <v>241500</v>
+        <v>17430</v>
       </c>
       <c r="L5" t="n">
-        <v>244000</v>
+        <v>17730</v>
       </c>
       <c r="M5" t="n">
-        <v>238000</v>
+        <v>17290</v>
       </c>
       <c r="N5" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="O5" t="n">
-        <v>510705259000</v>
+        <v>12059616200</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q5" t="n">
-        <v>90200</v>
+        <v>17290</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,20 +902,20 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적인 게시글이 다수 확인되었으며, 거시 경제 전반에 대한 비관적인 전망이 제시되었습니다.</t>
+          <t>정치적 요인과 증권사 목표가에 대한 언급, 삼성중공업 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['목표가', '주가 하락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1523000</v>
+        <v>69200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-5.11%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>133</v>
       </c>
       <c r="F6" t="n">
-        <v>532</v>
+        <v>101</v>
       </c>
       <c r="G6" t="n">
-        <v>1990</v>
+        <v>434</v>
       </c>
       <c r="H6" t="n">
-        <v>49.41</v>
+        <v>22.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1605000</v>
+        <v>71500</v>
       </c>
       <c r="K6" t="n">
-        <v>1538000</v>
+        <v>68400</v>
       </c>
       <c r="L6" t="n">
-        <v>1554000</v>
+        <v>70000</v>
       </c>
       <c r="M6" t="n">
-        <v>1519000</v>
+        <v>68000</v>
       </c>
       <c r="N6" t="n">
-        <v>49.52</v>
+        <v>22.21</v>
       </c>
       <c r="O6" t="n">
-        <v>665814277000</v>
+        <v>32474348100</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>139200</v>
       </c>
       <c r="Q6" t="n">
-        <v>403000</v>
+        <v>57000</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>192000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>정치적 요인과 관련된 부정적인 언급이 지배적이며, 증시 붕괴 및 주가 폭락에 대한 비관적인 전망이 다수 확인되었습니다.</t>
+          <t>두산에너빌리티 주가 하락에 대한 실망감과 정치적 요인에 대한 비판.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['증시 붕괴', '주가 폭락']</t>
+          <t>['주가 하락', '원전주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6460</v>
+        <v>15550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-5.14%</t>
+          <t>'-3.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.3</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="H7" t="n">
-        <v>12.27</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>6810</v>
+        <v>16090</v>
       </c>
       <c r="K7" t="n">
-        <v>7150</v>
+        <v>15190</v>
       </c>
       <c r="L7" t="n">
-        <v>7160</v>
+        <v>15830</v>
       </c>
       <c r="M7" t="n">
-        <v>6450</v>
+        <v>15100</v>
       </c>
       <c r="N7" t="n">
-        <v>12.57</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>8267694020</v>
+        <v>11856982395</v>
       </c>
       <c r="P7" t="n">
-        <v>8850</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>4220</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1086,20 +1086,20 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>공매도 관련 언급과 함께 주가 상승에 대한 기대감이 나타났으며, 일부 뉴스를 근거로 제시했습니다.</t>
+          <t>대우건설 주가 하락에 대한 우려와 시장 상황에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['공매도', '주가 상승']</t>
+          <t>['주가 하락', '시장 상황']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,67 +1108,67 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14840</v>
+        <v>237500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-5.60%</t>
+          <t>'-5.19%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>572</v>
       </c>
       <c r="G8" t="n">
-        <v>154</v>
+        <v>1866</v>
       </c>
       <c r="H8" t="n">
-        <v>3.43</v>
+        <v>46.3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>15720</v>
+        <v>250500</v>
       </c>
       <c r="K8" t="n">
-        <v>14770</v>
+        <v>241500</v>
       </c>
       <c r="L8" t="n">
-        <v>15060</v>
+        <v>244000</v>
       </c>
       <c r="M8" t="n">
-        <v>14420</v>
+        <v>236500</v>
       </c>
       <c r="N8" t="n">
-        <v>3.37</v>
+        <v>46.35</v>
       </c>
       <c r="O8" t="n">
-        <v>18880768220</v>
+        <v>755614079250</v>
       </c>
       <c r="P8" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>1272</v>
+        <v>90200</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 업체 기술력 및 AI 거품론 언급과 함께 주가 하락에 대한 우려가 제기되었으며, 일부 실적 관련 긍정적 언급도 있었습니다.</t>
+          <t>이재명 정부의 경제 정책 실패로 인한 대한민국 증시 및 삼성전자 주가 하락에 대한 비판.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기술력', 'AI 거품론', '실적']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,191 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14890</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'-5.28%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" t="n">
+        <v>49</v>
+      </c>
+      <c r="F9" t="n">
+        <v>34</v>
+      </c>
+      <c r="G9" t="n">
+        <v>173</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>15720</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14770</v>
+      </c>
+      <c r="L9" t="n">
+        <v>15130</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14420</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O9" t="n">
+        <v>26079495230</v>
+      </c>
+      <c r="P9" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>미국 광케이블 업체 하락 및 대한광통신 실적 발표 후 주가 하락에 대한 부정적 전망.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['광케이블', '실적']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1507000</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>'-6.11%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>800</v>
+      </c>
+      <c r="F10" t="n">
+        <v>553</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1804</v>
+      </c>
+      <c r="H10" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1504000</v>
+      </c>
+      <c r="N10" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O10" t="n">
+        <v>975445053500</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-246000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>정치적 요인으로 인한 SK하이닉스 및 대한민국 증시 폭락에 대한 강한 부정적 인식.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>000660</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261013_09.xlsx
+++ b/data/trending_integrated_20261013_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>78898036450</v>
+        <v>85480837890</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -619,14 +619,14 @@
         <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-80000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 투자 관련 수혜주로 서산의 주가 상승 기대감 및 긍정적 전망.</t>
+          <t>호남 반도체 클러스터 관련 수혜주로 부각. 연이은 상한가 기록 및 3만 전자 목표.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남 반도체', '수혜주', '주가 상승']</t>
+          <t>['호남반도체', '수혜주', '연상']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,70 +655,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43550</v>
+        <v>13480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'+21.77%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.23</v>
+        <v>0.92</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>395</v>
+        <v>81</v>
       </c>
       <c r="H3" t="n">
-        <v>13.1</v>
+        <v>15.64</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>44400</v>
+        <v>11070</v>
       </c>
       <c r="K3" t="n">
-        <v>43300</v>
+        <v>11670</v>
       </c>
       <c r="L3" t="n">
-        <v>44100</v>
+        <v>13970</v>
       </c>
       <c r="M3" t="n">
-        <v>42500</v>
+        <v>11200</v>
       </c>
       <c r="N3" t="n">
-        <v>13.33</v>
+        <v>14.72</v>
       </c>
       <c r="O3" t="n">
-        <v>5559327675</v>
+        <v>158373965485</v>
       </c>
       <c r="P3" t="n">
-        <v>69200</v>
+        <v>14350</v>
       </c>
       <c r="Q3" t="n">
-        <v>24150</v>
+        <v>465</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-149000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>HLB의 간암 1차 승인 기대감과 공매도 세력에 대한 언급, 긍정적 전망.</t>
+          <t>호남 반도체 클러스터 관련 테마 상승 기대감. 관리종목 해제 및 10만 전자 목표.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['간암 1차 승인', '공매도']</t>
+          <t>['호남클러스터', '반도체', '관리종목해제']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6630</v>
+        <v>15110</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-2.64%</t>
+          <t>'+12.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.3</v>
+        <v>-1.01</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="H4" t="n">
-        <v>12.27</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>6810</v>
+        <v>13400</v>
       </c>
       <c r="K4" t="n">
-        <v>7150</v>
+        <v>13750</v>
       </c>
       <c r="L4" t="n">
-        <v>7160</v>
+        <v>15390</v>
       </c>
       <c r="M4" t="n">
-        <v>6440</v>
+        <v>12380</v>
       </c>
       <c r="N4" t="n">
-        <v>12.57</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>9887777415</v>
+        <v>84840553145</v>
       </c>
       <c r="P4" t="n">
-        <v>8850</v>
+        <v>19380</v>
       </c>
       <c r="Q4" t="n">
-        <v>4220</v>
+        <v>3200</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호타이어 주가 부양에 대한 기대감과 공매도 세력에 대한 비판.</t>
+          <t>서산과 연계된 반도체 테마 상승 기대감. 삼성, SK 관련 호남 투자 이슈.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공매도', '부양']</t>
+          <t>['반도체', '호남', '삼성SK']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17530</v>
+        <v>14250</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.67%</t>
+          <t>'+6.26%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E5" t="n">
         <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>154</v>
+        <v>81</v>
       </c>
       <c r="H5" t="n">
-        <v>27.69</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>18010</v>
+        <v>13410</v>
       </c>
       <c r="K5" t="n">
-        <v>17430</v>
+        <v>13260</v>
       </c>
       <c r="L5" t="n">
-        <v>17730</v>
+        <v>14580</v>
       </c>
       <c r="M5" t="n">
-        <v>17290</v>
+        <v>13250</v>
       </c>
       <c r="N5" t="n">
-        <v>27.61</v>
+        <v>0.21</v>
       </c>
       <c r="O5" t="n">
-        <v>12059616200</v>
+        <v>26476552270</v>
       </c>
       <c r="P5" t="n">
-        <v>35350</v>
+        <v>28700</v>
       </c>
       <c r="Q5" t="n">
-        <v>17290</v>
+        <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>정치적 요인과 증권사 목표가에 대한 언급, 삼성중공업 주가 하락에 대한 부정적 전망.</t>
+          <t>종목명과 관련된 내용이 부실하여 분석 불가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['목표가', '주가 하락']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69200</v>
+        <v>6680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.22%</t>
+          <t>'-1.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.11</v>
+        <v>-0.3</v>
       </c>
       <c r="E6" t="n">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="F6" t="n">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>434</v>
+        <v>291</v>
       </c>
       <c r="H6" t="n">
-        <v>22.1</v>
+        <v>12.27</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>71500</v>
+        <v>6810</v>
       </c>
       <c r="K6" t="n">
-        <v>68400</v>
+        <v>7150</v>
       </c>
       <c r="L6" t="n">
-        <v>70000</v>
+        <v>7160</v>
       </c>
       <c r="M6" t="n">
-        <v>68000</v>
+        <v>6440</v>
       </c>
       <c r="N6" t="n">
-        <v>22.21</v>
+        <v>12.57</v>
       </c>
       <c r="O6" t="n">
-        <v>32474348100</v>
+        <v>11814205350</v>
       </c>
       <c r="P6" t="n">
-        <v>139200</v>
+        <v>8850</v>
       </c>
       <c r="Q6" t="n">
-        <v>57000</v>
+        <v>4220</v>
       </c>
       <c r="R6" t="n">
-        <v>192000</v>
+        <v>-629000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>두산에너빌리티 주가 하락에 대한 실망감과 정치적 요인에 대한 비판.</t>
+          <t>의도적인 주가 누르기에 대한 불만. 공매도 관련 이슈 및 광주 조감도 호재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 하락', '원전주']</t>
+          <t>['공매도', '주가누르기', '광주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15550</v>
+        <v>17590</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.36%</t>
+          <t>'-2.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="H7" t="n">
-        <v>9.630000000000001</v>
+        <v>27.69</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16090</v>
+        <v>18010</v>
       </c>
       <c r="K7" t="n">
-        <v>15190</v>
+        <v>17430</v>
       </c>
       <c r="L7" t="n">
-        <v>15830</v>
+        <v>17730</v>
       </c>
       <c r="M7" t="n">
-        <v>15100</v>
+        <v>17290</v>
       </c>
       <c r="N7" t="n">
-        <v>9.470000000000001</v>
+        <v>27.61</v>
       </c>
       <c r="O7" t="n">
-        <v>11856982395</v>
+        <v>15335302560</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>17290</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>231000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설 주가 하락에 대한 우려와 시장 상황에 대한 부정적 전망.</t>
+          <t>정치적 이슈와 증시 하락 연관성 언급. 데이터 센터, 주주 불만 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 하락', '시장 상황']</t>
+          <t>['민주당', '데이터센터', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>237500</v>
+        <v>15640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-5.19%</t>
+          <t>'-2.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>572</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>1866</v>
+        <v>139</v>
       </c>
       <c r="H8" t="n">
-        <v>46.3</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>250500</v>
+        <v>16090</v>
       </c>
       <c r="K8" t="n">
-        <v>241500</v>
+        <v>15190</v>
       </c>
       <c r="L8" t="n">
-        <v>244000</v>
+        <v>15830</v>
       </c>
       <c r="M8" t="n">
-        <v>236500</v>
+        <v>15100</v>
       </c>
       <c r="N8" t="n">
-        <v>46.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>755614079250</v>
+        <v>14428585960</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>154000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>이재명 정부의 경제 정책 실패로 인한 대한민국 증시 및 삼성전자 주가 하락에 대한 비판.</t>
+          <t>개인 투자자들의 불만 표출. 국장 전반의 하락세 및 개별 종목의 어려움.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['국장', '하락세', '뱅크런']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14890</v>
+        <v>7530</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-5.28%</t>
+          <t>'-2.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="H9" t="n">
-        <v>3.43</v>
+        <v>26.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>15720</v>
+        <v>7760</v>
       </c>
       <c r="K9" t="n">
-        <v>14770</v>
+        <v>7650</v>
       </c>
       <c r="L9" t="n">
-        <v>15130</v>
+        <v>7680</v>
       </c>
       <c r="M9" t="n">
-        <v>14420</v>
+        <v>7470</v>
       </c>
       <c r="N9" t="n">
-        <v>3.37</v>
+        <v>26.37</v>
       </c>
       <c r="O9" t="n">
-        <v>26079495230</v>
+        <v>4889401535</v>
       </c>
       <c r="P9" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>1272</v>
+        <v>7470</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-113000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 광케이블 업체 하락 및 대한광통신 실적 발표 후 주가 하락에 대한 부정적 전망.</t>
+          <t>기업의 재무 상태 및 향후 전망에 대한 부정적 의견. 상폐 및 적자 관련 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['광케이블', '실적']</t>
+          <t>['적자', '상폐', '재무상태']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,97 +1292,465 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1507000</v>
+        <v>43050</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-6.11%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>553</v>
+        <v>61</v>
       </c>
       <c r="G10" t="n">
-        <v>1804</v>
+        <v>403</v>
       </c>
       <c r="H10" t="n">
-        <v>49.41</v>
+        <v>13.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1605000</v>
+        <v>44400</v>
       </c>
       <c r="K10" t="n">
-        <v>1538000</v>
+        <v>43300</v>
       </c>
       <c r="L10" t="n">
-        <v>1554000</v>
+        <v>44100</v>
       </c>
       <c r="M10" t="n">
-        <v>1504000</v>
+        <v>42500</v>
       </c>
       <c r="N10" t="n">
-        <v>49.52</v>
+        <v>13.33</v>
       </c>
       <c r="O10" t="n">
-        <v>975445053500</v>
+        <v>6606738300</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>403000</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-246000</v>
+        <v>31000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 요인으로 인한 SK하이닉스 및 대한민국 증시 폭락에 대한 강한 부정적 인식.</t>
+          <t>HLB 공매도 관련 내용과 간암 1차 승인 기대감 언급. 긍정적 전망과 악재 가능성 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['공매도', '간암', '승인']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>028300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>두산에너빌리티</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>69200</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-3.22%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>139</v>
+      </c>
+      <c r="F11" t="n">
+        <v>105</v>
+      </c>
+      <c r="G11" t="n">
+        <v>436</v>
+      </c>
+      <c r="H11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>71500</v>
+      </c>
+      <c r="K11" t="n">
+        <v>68400</v>
+      </c>
+      <c r="L11" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M11" t="n">
+        <v>68000</v>
+      </c>
+      <c r="N11" t="n">
+        <v>22.21</v>
+      </c>
+      <c r="O11" t="n">
+        <v>39658439150</v>
+      </c>
+      <c r="P11" t="n">
+        <v>139200</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R11" t="n">
+        <v>192000</v>
+      </c>
+      <c r="S11" t="n">
         <v>0</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X10" t="n">
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>두산에너빌리티 주가 하락에 대한 실망감과 정치적 요인에 대한 비판.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['주가 하락', '원전주']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>14990</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-4.64%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>55</v>
+      </c>
+      <c r="F12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G12" t="n">
+        <v>188</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>15720</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14770</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15130</v>
+      </c>
+      <c r="M12" t="n">
+        <v>14420</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="O12" t="n">
+        <v>29929125205</v>
+      </c>
+      <c r="P12" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R12" t="n">
+        <v>177000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>미국 업체 기술력 하락 및 AI 거품론 관련 우려. 분기별 어닝 서프라이즈에도 주가 하락.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['광케이블', 'AI거품론', '어닝서프라이즈']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>10</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>236500</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-5.59%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E13" t="n">
+        <v>800</v>
+      </c>
+      <c r="F13" t="n">
+        <v>572</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1831</v>
+      </c>
+      <c r="H13" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>250500</v>
+      </c>
+      <c r="K13" t="n">
+        <v>241500</v>
+      </c>
+      <c r="L13" t="n">
+        <v>244000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>236500</v>
+      </c>
+      <c r="N13" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="O13" t="n">
+        <v>907621826000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-909000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>현 정부 정책에 대한 강한 불만 표출. 정치적 요인으로 인한 주가 하락 우려.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['이재명', '정치', '주가하락']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1499000</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-6.60%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>800</v>
+      </c>
+      <c r="F14" t="n">
+        <v>558</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1693</v>
+      </c>
+      <c r="H14" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1498000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1226717138000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-246000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>정치적 요인과 증시 하락 연관성 강하게 제기. 호남 반도체 이슈에 대한 부정적 시각.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['이재명', '호남반도체', '증시붕괴']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>000660</t>
         </is>

--- a/data/trending_integrated_20261013_09.xlsx
+++ b/data/trending_integrated_20261013_09.xlsx
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>85480837890</v>
+        <v>85830176530</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 관련 수혜주로 부각. 연이은 상한가 기록 및 3만 전자 목표.</t>
+          <t>호남 반도체, 전남광주 경제자유구역 확대 추진 수혜주. 무차입 경영, 10년 만의 고점 돌파 시도.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '수혜주', '연상']</t>
+          <t>['호남반도체', '경제자유구역', '무차입경영']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13480</v>
+        <v>13420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.77%</t>
+          <t>'+21.23%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.92</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="H3" t="n">
         <v>15.64</v>
@@ -702,7 +702,7 @@
         <v>14.72</v>
       </c>
       <c r="O3" t="n">
-        <v>158373965485</v>
+        <v>185960018610</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>호남 반도체 클러스터 관련 테마 상승 기대감. 관리종목 해제 및 10만 전자 목표.</t>
+          <t>호남 클러스터 테마 외 모든 테마 사망. 인생 역전 주식으로 800% 상승 기대. 토스, 미래에셋 매수세 유입.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['호남클러스터', '반도체', '관리종목해제']</t>
+          <t>['인생역전', '호남클러스터', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15110</v>
+        <v>14830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.76%</t>
+          <t>'+10.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-1.01</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         <v>1.01</v>
       </c>
       <c r="O4" t="n">
-        <v>84840553145</v>
+        <v>107265099780</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>서산과 연계된 반도체 테마 상승 기대감. 삼성, SK 관련 호남 투자 이슈.</t>
+          <t>호남 반도체 사업 속도전 관련 삼성, SK 기업 운명 걸림. 금호건설이 대장이나 서산에 밀리는 모습.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '호남', '삼성SK']</t>
+          <t>['호남반도체', '속도전', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14250</v>
+        <v>14200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.26%</t>
+          <t>'+5.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.09</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G5" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.21</v>
       </c>
       <c r="O5" t="n">
-        <v>26476552270</v>
+        <v>31204792975</v>
       </c>
       <c r="P5" t="n">
         <v>28700</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>종목명과 관련된 내용이 부실하여 분석 불가.</t>
+          <t>대차 상환 및 공매도 관련 언급. 3일째 전강약후, 종가 하락 예상. 주포 및 단타 맛집 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['대차상환', '공매도', '전강약후']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6680</v>
+        <v>17630</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.91%</t>
+          <t>'-2.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.3</v>
+        <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>291</v>
+        <v>163</v>
       </c>
       <c r="H6" t="n">
-        <v>12.27</v>
+        <v>27.69</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>6810</v>
+        <v>18010</v>
       </c>
       <c r="K6" t="n">
-        <v>7150</v>
+        <v>17430</v>
       </c>
       <c r="L6" t="n">
-        <v>7160</v>
+        <v>17730</v>
       </c>
       <c r="M6" t="n">
-        <v>6440</v>
+        <v>17290</v>
       </c>
       <c r="N6" t="n">
-        <v>12.57</v>
+        <v>27.61</v>
       </c>
       <c r="O6" t="n">
-        <v>11814205350</v>
+        <v>17563518750</v>
       </c>
       <c r="P6" t="n">
-        <v>8850</v>
+        <v>35350</v>
       </c>
       <c r="Q6" t="n">
-        <v>4220</v>
+        <v>17290</v>
       </c>
       <c r="R6" t="n">
-        <v>-629000</v>
+        <v>231000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기에 대한 불만. 공매도 관련 이슈 및 광주 조감도 호재.</t>
+          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 민주당 정부 관련 부정적 언급 다수.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['공매도', '주가누르기', '광주']</t>
+          <t>['FLNG', '매출전망', '목표가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17590</v>
+        <v>15710</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-2.36%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F7" t="n">
         <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="H7" t="n">
-        <v>27.69</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18010</v>
+        <v>16090</v>
       </c>
       <c r="K7" t="n">
-        <v>17430</v>
+        <v>15190</v>
       </c>
       <c r="L7" t="n">
-        <v>17730</v>
+        <v>15830</v>
       </c>
       <c r="M7" t="n">
-        <v>17290</v>
+        <v>15100</v>
       </c>
       <c r="N7" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>15335302560</v>
+        <v>16738181915</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>17290</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>231000</v>
+        <v>154000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 이슈와 증시 하락 연관성 언급. 데이터 센터, 주주 불만 표출.</t>
+          <t>개인 투자자들의 불만 표출. 국장 전반의 하락세 및 개별 종목의 어려움.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['민주당', '데이터센터', '주가']</t>
+          <t>['국장', '하락세', '뱅크런']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15640</v>
+        <v>69600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.80%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>111</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>441</v>
       </c>
       <c r="H8" t="n">
-        <v>9.630000000000001</v>
+        <v>22.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16090</v>
+        <v>71500</v>
       </c>
       <c r="K8" t="n">
-        <v>15190</v>
+        <v>68400</v>
       </c>
       <c r="L8" t="n">
-        <v>15830</v>
+        <v>70000</v>
       </c>
       <c r="M8" t="n">
-        <v>15100</v>
+        <v>68000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.470000000000001</v>
+        <v>22.21</v>
       </c>
       <c r="O8" t="n">
-        <v>14428585960</v>
+        <v>45068283300</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>154000</v>
+        <v>192000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>개인 투자자들의 불만 표출. 국장 전반의 하락세 및 개별 종목의 어려움.</t>
+          <t>두산에너빌리티, 주가 하락 및 신용 매매 관련 언급. 정치적 요인과 시장 상황에 대한 부정적 인식이 주를 이룸.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국장', '하락세', '뱅크런']</t>
+          <t>['반대매매', '신용', '원전주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7530</v>
+        <v>7500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.96%</t>
+          <t>'-3.35%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.36</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H9" t="n">
         <v>26.01</v>
@@ -1254,7 +1254,7 @@
         <v>26.37</v>
       </c>
       <c r="O9" t="n">
-        <v>4889401535</v>
+        <v>5550280725</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기업의 재무 상태 및 향후 전망에 대한 부정적 의견. 상폐 및 적자 관련 우려.</t>
+          <t>아이폰 패널 출하량 감소 및 미장 ADR 폭락 언급. 나라 경제 위해 상폐 주장, 4분기 프로 모델 물량 공급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['적자', '상폐', '재무상태']</t>
+          <t>['아이폰패널', '출하량감소', '상폐']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43050</v>
+        <v>6570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'-3.52%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.23</v>
+        <v>-0.3</v>
       </c>
       <c r="E10" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>403</v>
+        <v>309</v>
       </c>
       <c r="H10" t="n">
-        <v>13.1</v>
+        <v>12.27</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>44400</v>
+        <v>6810</v>
       </c>
       <c r="K10" t="n">
-        <v>43300</v>
+        <v>7150</v>
       </c>
       <c r="L10" t="n">
-        <v>44100</v>
+        <v>7160</v>
       </c>
       <c r="M10" t="n">
-        <v>42500</v>
+        <v>6440</v>
       </c>
       <c r="N10" t="n">
-        <v>13.33</v>
+        <v>12.57</v>
       </c>
       <c r="O10" t="n">
-        <v>6606738300</v>
+        <v>13262813150</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>8850</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>4220</v>
       </c>
       <c r="R10" t="n">
-        <v>31000</v>
+        <v>-629000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB 공매도 관련 내용과 간암 1차 승인 기대감 언급. 긍정적 전망과 악재 가능성 혼재.</t>
+          <t>의도적인 주가 누르기 및 공매도 의혹 제기. 금감원 개입 촉구. 광주 조감도 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '간암', '승인']</t>
+          <t>['공매도', '누르기', '광주조감도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>42800</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>'-3.60%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E11" t="n">
+        <v>99</v>
+      </c>
+      <c r="F11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G11" t="n">
+        <v>416</v>
+      </c>
+      <c r="H11" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>44400</v>
+      </c>
+      <c r="K11" t="n">
+        <v>43300</v>
+      </c>
+      <c r="L11" t="n">
+        <v>44100</v>
+      </c>
+      <c r="M11" t="n">
+        <v>42500</v>
+      </c>
+      <c r="N11" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7673119825</v>
+      </c>
+      <c r="P11" t="n">
         <v>69200</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>'-3.22%</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="E11" t="n">
-        <v>139</v>
-      </c>
-      <c r="F11" t="n">
-        <v>105</v>
-      </c>
-      <c r="G11" t="n">
-        <v>436</v>
-      </c>
-      <c r="H11" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>71500</v>
-      </c>
-      <c r="K11" t="n">
-        <v>68400</v>
-      </c>
-      <c r="L11" t="n">
-        <v>70000</v>
-      </c>
-      <c r="M11" t="n">
-        <v>68000</v>
-      </c>
-      <c r="N11" t="n">
-        <v>22.21</v>
-      </c>
-      <c r="O11" t="n">
-        <v>39658439150</v>
-      </c>
-      <c r="P11" t="n">
-        <v>139200</v>
-      </c>
       <c r="Q11" t="n">
-        <v>57000</v>
+        <v>24150</v>
       </c>
       <c r="R11" t="n">
-        <v>192000</v>
+        <v>31000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>두산에너빌리티 주가 하락에 대한 실망감과 정치적 요인에 대한 비판.</t>
+          <t>HLB, 리보&amp;캄렐 간암 1차 승인 기대감 속 매물대 소화 및 통합 IR 데이 예정. 일부 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '원전주']</t>
+          <t>['리보', '캄렐', 'IR 데이']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14990</v>
+        <v>15010</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.64%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="H12" t="n">
         <v>3.43</v>
@@ -1530,7 +1530,7 @@
         <v>3.37</v>
       </c>
       <c r="O12" t="n">
-        <v>29929125205</v>
+        <v>33092204110</v>
       </c>
       <c r="P12" t="n">
         <v>31500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 업체 기술력 하락 및 AI 거품론 관련 우려. 분기별 어닝 서프라이즈에도 주가 하락.</t>
+          <t>3분기 어닝 서프라이즈 (매출 668억, 영업이익 59억). 미국 업체 기술력 하락 및 AI 거품론으로 인한 하락 우려.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['광케이블', 'AI거품론', '어닝서프라이즈']</t>
+          <t>['어닝서프라이즈', '광케이블', 'AI거품론']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>236500</v>
+        <v>237250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.59%</t>
+          <t>'-5.29%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G13" t="n">
-        <v>1831</v>
+        <v>1774</v>
       </c>
       <c r="H13" t="n">
         <v>46.3</v>
@@ -1616,13 +1616,13 @@
         <v>244000</v>
       </c>
       <c r="M13" t="n">
-        <v>236500</v>
+        <v>236000</v>
       </c>
       <c r="N13" t="n">
         <v>46.35</v>
       </c>
       <c r="O13" t="n">
-        <v>907621826000</v>
+        <v>1054089564000</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>현 정부 정책에 대한 강한 불만 표출. 정치적 요인으로 인한 주가 하락 우려.</t>
+          <t>정부 정책 및 이재명 관련 부정적 언급 다수. 수백조 영업이익에도 주가 부진, 투자자들의 불만 고조.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['이재명', '정치', '주가하락']</t>
+          <t>['이재명', '주가부진', '정부정책']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1499000</v>
+        <v>1510000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.60%</t>
+          <t>'-5.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="G14" t="n">
-        <v>1693</v>
+        <v>1556</v>
       </c>
       <c r="H14" t="n">
         <v>49.41</v>
@@ -1708,13 +1708,13 @@
         <v>1554000</v>
       </c>
       <c r="M14" t="n">
-        <v>1498000</v>
+        <v>1496000</v>
       </c>
       <c r="N14" t="n">
         <v>49.52</v>
       </c>
       <c r="O14" t="n">
-        <v>1226717138000</v>
+        <v>1471326101500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정치적 요인과 증시 하락 연관성 강하게 제기. 호남 반도체 이슈에 대한 부정적 시각.</t>
+          <t>이재명, 전라도 반도체 등 정치적 이슈로 인한 증시 붕괴 우려. 성과급 반납 요구 및 경영진 비판.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재명', '호남반도체', '증시붕괴']</t>
+          <t>['이재명', '전라도반도체', '증시붕괴']</t>
         </is>
       </c>
       <c r="X14" t="n">

--- a/data/trending_integrated_20261013_09.xlsx
+++ b/data/trending_integrated_20261013_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.57</v>
       </c>
       <c r="E2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H2" t="n">
         <v>1.84</v>
@@ -610,7 +610,7 @@
         <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>85830176530</v>
+        <v>86031642410</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>호남 반도체, 전남광주 경제자유구역 확대 추진 수혜주. 무차입 경영, 10년 만의 고점 돌파 시도.</t>
+          <t>호남 반도체 클러스터 및 광주 신도시 개발 수혜 기대. 10년 만에 뚫린 자리, 대장주로서의 귀환 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['호남반도체', '경제자유구역', '무차입경영']</t>
+          <t>['호남반도체', '클러스터', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13420</v>
+        <v>13110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.23%</t>
+          <t>'+18.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.92</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H3" t="n">
         <v>15.64</v>
@@ -702,7 +702,7 @@
         <v>14.72</v>
       </c>
       <c r="O3" t="n">
-        <v>185960018610</v>
+        <v>201608580775</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>호남 클러스터 테마 외 모든 테마 사망. 인생 역전 주식으로 800% 상승 기대. 토스, 미래에셋 매수세 유입.</t>
+          <t>호남 클러스터 테마 외 모든 테마 소멸 전망. 13650원 매도 성공, 5만 원 목표. 시총 1600억, 영업이익 -21억.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['인생역전', '호남클러스터', '테마']</t>
+          <t>['호남클러스터', '반도체', '영업이익']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14830</v>
+        <v>18390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+10.67%</t>
+          <t>'+12.48%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.01</v>
+        <v>-0.25</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13400</v>
+        <v>16350</v>
       </c>
       <c r="K4" t="n">
-        <v>13750</v>
+        <v>15790</v>
       </c>
       <c r="L4" t="n">
-        <v>15390</v>
+        <v>18400</v>
       </c>
       <c r="M4" t="n">
-        <v>12380</v>
+        <v>15520</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="O4" t="n">
-        <v>107265099780</v>
+        <v>86648965665</v>
       </c>
       <c r="P4" t="n">
-        <v>19380</v>
+        <v>18400</v>
       </c>
       <c r="Q4" t="n">
-        <v>3200</v>
+        <v>6320</v>
       </c>
       <c r="R4" t="n">
-        <v>-70000</v>
+        <v>9000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>호남 반도체 사업 속도전 관련 삼성, SK 기업 운명 걸림. 금호건설이 대장이나 서산에 밀리는 모습.</t>
+          <t>미국 보안주 폭락 속 개별 상승 기대감, 신고가 재돌파 및 10% 이상 상승 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남반도체', '속도전', '대장주']</t>
+          <t>['보안주', '신고가', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14200</v>
+        <v>14390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+5.89%</t>
+          <t>'+7.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09</v>
+        <v>-1.01</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13410</v>
+        <v>13400</v>
       </c>
       <c r="K5" t="n">
-        <v>13260</v>
+        <v>13750</v>
       </c>
       <c r="L5" t="n">
-        <v>14580</v>
+        <v>15390</v>
       </c>
       <c r="M5" t="n">
-        <v>13250</v>
+        <v>12380</v>
       </c>
       <c r="N5" t="n">
-        <v>0.21</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>31204792975</v>
+        <v>118630080575</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>19380</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>3200</v>
       </c>
       <c r="R5" t="n">
-        <v>30000</v>
+        <v>-70000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>대차 상환 및 공매도 관련 언급. 3일째 전강약후, 종가 하락 예상. 주포 및 단타 맛집 언급.</t>
+          <t>호남 반도체 사업 관련 삼성, SK 기업 운명 걸었다는 분석. 서산과 함께 금호건설이 대장이라는 의견.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['대차상환', '공매도', '전강약후']</t>
+          <t>['호남반도체', '삼성', 'SK']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17630</v>
+        <v>13830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.11%</t>
+          <t>'+3.13%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="H6" t="n">
-        <v>27.69</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>18010</v>
+        <v>13410</v>
       </c>
       <c r="K6" t="n">
-        <v>17430</v>
+        <v>13260</v>
       </c>
       <c r="L6" t="n">
-        <v>17730</v>
+        <v>14580</v>
       </c>
       <c r="M6" t="n">
-        <v>17290</v>
+        <v>13250</v>
       </c>
       <c r="N6" t="n">
-        <v>27.61</v>
+        <v>0.21</v>
       </c>
       <c r="O6" t="n">
-        <v>17563518750</v>
+        <v>33821175040</v>
       </c>
       <c r="P6" t="n">
-        <v>35350</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>17290</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>231000</v>
+        <v>30000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 민주당 정부 관련 부정적 언급 다수.</t>
+          <t>대차 상환 및 공매도 상황 속에서 상승 기대감과 하락 전망이 혼재. 전강 후약 및 장 막판 하락 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FLNG', '매출전망', '목표가']</t>
+          <t>['대차', '공매도', '전강 후약']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15710</v>
+        <v>7300</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.36%</t>
+          <t>'-1.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="H7" t="n">
-        <v>9.630000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16090</v>
+        <v>7410</v>
       </c>
       <c r="K7" t="n">
-        <v>15190</v>
+        <v>7330</v>
       </c>
       <c r="L7" t="n">
-        <v>15830</v>
+        <v>8040</v>
       </c>
       <c r="M7" t="n">
-        <v>15100</v>
+        <v>6940</v>
       </c>
       <c r="N7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="O7" t="n">
-        <v>16738181915</v>
+        <v>48665796735</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>23500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2890</v>
       </c>
       <c r="R7" t="n">
-        <v>154000</v>
+        <v>-23000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>개인 투자자들의 불만 표출. 국장 전반의 하락세 및 개별 종목의 어려움.</t>
+          <t>호남 반도체 클러스터 신도시 개발 대장주로서의 기대감. 수도권 30% 점유율 및 거점 공장 보유.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['국장', '하락세', '뱅크런']</t>
+          <t>['호남반도체', '신도시개발', '점유율']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69600</v>
+        <v>15840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-1.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.11</v>
+        <v>0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>441</v>
+        <v>153</v>
       </c>
       <c r="H8" t="n">
-        <v>22.1</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>71500</v>
+        <v>16090</v>
       </c>
       <c r="K8" t="n">
-        <v>68400</v>
+        <v>15190</v>
       </c>
       <c r="L8" t="n">
-        <v>70000</v>
+        <v>15840</v>
       </c>
       <c r="M8" t="n">
-        <v>68000</v>
+        <v>15100</v>
       </c>
       <c r="N8" t="n">
-        <v>22.21</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>45068283300</v>
+        <v>18824851820</v>
       </c>
       <c r="P8" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>192000</v>
+        <v>154000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 주가 하락 및 신용 매매 관련 언급. 정치적 요인과 시장 상황에 대한 부정적 인식이 주를 이룸.</t>
+          <t>개인 투자자들의 고통과 시장 상황에 대한 부정적 전망. 도배글에 대한 불만. 건설 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반대매매', '신용', '원전주']</t>
+          <t>['시장상황', '개인투자자', '건설']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7500</v>
+        <v>17600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.35%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.36</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G9" t="n">
-        <v>117</v>
+        <v>168</v>
       </c>
       <c r="H9" t="n">
-        <v>26.01</v>
+        <v>27.69</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7760</v>
+        <v>18010</v>
       </c>
       <c r="K9" t="n">
-        <v>7650</v>
+        <v>17430</v>
       </c>
       <c r="L9" t="n">
-        <v>7680</v>
+        <v>17730</v>
       </c>
       <c r="M9" t="n">
-        <v>7470</v>
+        <v>17290</v>
       </c>
       <c r="N9" t="n">
-        <v>26.37</v>
+        <v>27.61</v>
       </c>
       <c r="O9" t="n">
-        <v>5550280725</v>
+        <v>20186931755</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>7470</v>
+        <v>17290</v>
       </c>
       <c r="R9" t="n">
-        <v>-113000</v>
+        <v>231000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>아이폰 패널 출하량 감소 및 미장 ADR 폭락 언급. 나라 경제 위해 상폐 주장, 4분기 프로 모델 물량 공급.</t>
+          <t>FLNG 매출 3.2조 확대 전망 및 목표가 42,000원 제시. 민주당 정권 및 공매도에 대한 비판.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['아이폰패널', '출하량감소', '상폐']</t>
+          <t>['FLNG', '매출전망', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금호타이어</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6570</v>
+        <v>69600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.52%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3</v>
+        <v>-0.11</v>
       </c>
       <c r="E10" t="n">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="F10" t="n">
-        <v>58</v>
+        <v>108</v>
       </c>
       <c r="G10" t="n">
-        <v>309</v>
+        <v>461</v>
       </c>
       <c r="H10" t="n">
-        <v>12.27</v>
+        <v>22.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6810</v>
+        <v>71500</v>
       </c>
       <c r="K10" t="n">
-        <v>7150</v>
+        <v>68400</v>
       </c>
       <c r="L10" t="n">
-        <v>7160</v>
+        <v>70000</v>
       </c>
       <c r="M10" t="n">
-        <v>6440</v>
+        <v>68000</v>
       </c>
       <c r="N10" t="n">
-        <v>12.57</v>
+        <v>22.21</v>
       </c>
       <c r="O10" t="n">
-        <v>13262813150</v>
+        <v>48992431350</v>
       </c>
       <c r="P10" t="n">
-        <v>8850</v>
+        <v>139200</v>
       </c>
       <c r="Q10" t="n">
-        <v>4220</v>
+        <v>57000</v>
       </c>
       <c r="R10" t="n">
-        <v>-629000</v>
+        <v>192000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>의도적인 주가 누르기 및 공매도 의혹 제기. 금감원 개입 촉구. 광주 조감도 관련 뉴스 언급.</t>
+          <t>정치적 이슈 및 신용 반대매매 쏟아지며 57000원 지지선 붕괴 우려. 원전주 전반의 하락세.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '누르기', '광주조감도']</t>
+          <t>['신용 반대매매', '원전주', '지지선 붕괴']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>073240</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42800</v>
+        <v>7510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.60%</t>
+          <t>'-3.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.23</v>
+        <v>-0.36</v>
       </c>
       <c r="E11" t="n">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>416</v>
+        <v>138</v>
       </c>
       <c r="H11" t="n">
-        <v>13.1</v>
+        <v>26.01</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>44400</v>
+        <v>7760</v>
       </c>
       <c r="K11" t="n">
-        <v>43300</v>
+        <v>7650</v>
       </c>
       <c r="L11" t="n">
-        <v>44100</v>
+        <v>7680</v>
       </c>
       <c r="M11" t="n">
-        <v>42500</v>
+        <v>7440</v>
       </c>
       <c r="N11" t="n">
-        <v>13.33</v>
+        <v>26.37</v>
       </c>
       <c r="O11" t="n">
-        <v>7673119825</v>
+        <v>6808744215</v>
       </c>
       <c r="P11" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>24150</v>
+        <v>7440</v>
       </c>
       <c r="R11" t="n">
-        <v>31000</v>
+        <v>-113000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>HLB, 리보&amp;캄렐 간암 1차 승인 기대감 속 매물대 소화 및 통합 IR 데이 예정. 일부 부정적 전망도 존재.</t>
+          <t>지속적인 저점 갱신 및 적자 심화로 인한 상장폐지 가능성 제기. 아이폰 출하량 관련 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['리보', '캄렐', 'IR 데이']</t>
+          <t>['저점갱신', '적자', '아이폰']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>금호타이어</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15010</v>
+        <v>6570</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-3.52%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06</v>
+        <v>-0.3</v>
       </c>
       <c r="E12" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="G12" t="n">
-        <v>207</v>
+        <v>350</v>
       </c>
       <c r="H12" t="n">
-        <v>3.43</v>
+        <v>12.27</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15720</v>
+        <v>6810</v>
       </c>
       <c r="K12" t="n">
-        <v>14770</v>
+        <v>7150</v>
       </c>
       <c r="L12" t="n">
-        <v>15130</v>
+        <v>7160</v>
       </c>
       <c r="M12" t="n">
-        <v>14420</v>
+        <v>6440</v>
       </c>
       <c r="N12" t="n">
-        <v>3.37</v>
+        <v>12.57</v>
       </c>
       <c r="O12" t="n">
-        <v>33092204110</v>
+        <v>14090868575</v>
       </c>
       <c r="P12" t="n">
-        <v>31500</v>
+        <v>8850</v>
       </c>
       <c r="Q12" t="n">
-        <v>1272</v>
+        <v>4220</v>
       </c>
       <c r="R12" t="n">
-        <v>177000</v>
+        <v>-629000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3분기 어닝 서프라이즈 (매출 668억, 영업이익 59억). 미국 업체 기술력 하락 및 AI 거품론으로 인한 하락 우려.</t>
+          <t>공매도 및 의도적 누르기에 대한 불만 표출. 금감원 개입 촉구. 광주 조감도 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '광케이블', 'AI거품론']</t>
+          <t>['공매도', '누르기', '광주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>073240</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>237250</v>
+        <v>42750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-5.29%</t>
+          <t>'-3.72%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.05</v>
+        <v>-0.23</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>106</v>
       </c>
       <c r="F13" t="n">
-        <v>576</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>1774</v>
+        <v>435</v>
       </c>
       <c r="H13" t="n">
-        <v>46.3</v>
+        <v>13.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>250500</v>
+        <v>44400</v>
       </c>
       <c r="K13" t="n">
-        <v>241500</v>
+        <v>43300</v>
       </c>
       <c r="L13" t="n">
-        <v>244000</v>
+        <v>44100</v>
       </c>
       <c r="M13" t="n">
-        <v>236000</v>
+        <v>42500</v>
       </c>
       <c r="N13" t="n">
-        <v>46.35</v>
+        <v>13.33</v>
       </c>
       <c r="O13" t="n">
-        <v>1054089564000</v>
+        <v>8576727050</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>69200</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>24150</v>
       </c>
       <c r="R13" t="n">
-        <v>-909000</v>
+        <v>31000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정부 정책 및 이재명 관련 부정적 언급 다수. 수백조 영업이익에도 주가 부진, 투자자들의 불만 고조.</t>
+          <t>HLB, 리보&amp;캄렐 간암 1차 승인 기대감 속 매물대 소화 및 통합 IR 데이 예정. 일부 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['이재명', '주가부진', '정부정책']</t>
+          <t>['리보', '캄렐', 'IR 데이']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1510000</v>
+        <v>14970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-5.92%</t>
+          <t>'-4.77%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>62</v>
       </c>
       <c r="F14" t="n">
-        <v>570</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>1556</v>
+        <v>214</v>
       </c>
       <c r="H14" t="n">
-        <v>49.41</v>
+        <v>3.43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1605000</v>
+        <v>15720</v>
       </c>
       <c r="K14" t="n">
-        <v>1538000</v>
+        <v>14770</v>
       </c>
       <c r="L14" t="n">
-        <v>1554000</v>
+        <v>15130</v>
       </c>
       <c r="M14" t="n">
-        <v>1496000</v>
+        <v>14420</v>
       </c>
       <c r="N14" t="n">
-        <v>49.52</v>
+        <v>3.37</v>
       </c>
       <c r="O14" t="n">
-        <v>1471326101500</v>
+        <v>35840652100</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>403000</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-246000</v>
+        <v>177000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>이재명, 전라도 반도체 등 정치적 이슈로 인한 증시 붕괴 우려. 성과급 반납 요구 및 경영진 비판.</t>
+          <t>3분기 어닝 서프라이즈 발표에도 불구, 미국 업체 기술력 열세 및 AI 거품론으로 인한 하락 우려. 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['이재명', '전라도반도체', '증시붕괴']</t>
+          <t>['어닝 서프라이즈', '외인 매수', 'AI 거품론']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1751,6 +1751,190 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>237500</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-5.19%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E15" t="n">
+        <v>800</v>
+      </c>
+      <c r="F15" t="n">
+        <v>584</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1636</v>
+      </c>
+      <c r="H15" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>250500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>241500</v>
+      </c>
+      <c r="L15" t="n">
+        <v>244000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>236000</v>
+      </c>
+      <c r="N15" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1192224053000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>90200</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-909000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>정치적 불안정성 및 정부 정책 실패로 인한 국내 주식 시장 침체 우려. 이재명 관련 언급 다수.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['정치불안', '주식시장', '정책실패']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-5.92%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>800</v>
+      </c>
+      <c r="F16" t="n">
+        <v>565</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1469</v>
+      </c>
+      <c r="H16" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1538000</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1554000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1496000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1690287434500</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-246000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>정치 및 경제 정책 실패로 인한 증시 및 부동산 시장 불안정 심화 우려. 특정 지역 투자 관련 언급.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['정치리스크', '경제정책', '증시']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>000660</t>
         </is>
